--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848235</v>
       </c>
       <c r="B2" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128848230</v>
       </c>
       <c r="B3" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848235</v>
       </c>
       <c r="B2" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128848230</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848235</v>
       </c>
       <c r="B2" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128848230</v>
       </c>
       <c r="B3" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848235</v>
       </c>
       <c r="B2" t="n">
-        <v>100745</v>
+        <v>100750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128848230</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848235</v>
       </c>
       <c r="B2" t="n">
-        <v>100750</v>
+        <v>100753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128848230</v>
       </c>
       <c r="B3" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848235</v>
       </c>
       <c r="B2" t="n">
-        <v>100753</v>
+        <v>100763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128848230</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848235</v>
       </c>
       <c r="B2" t="n">
-        <v>100763</v>
+        <v>100770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128848230</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848235</v>
       </c>
       <c r="B2" t="n">
-        <v>100770</v>
+        <v>100772</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128848230</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848235</v>
       </c>
       <c r="B2" t="n">
-        <v>100772</v>
+        <v>100798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128848230</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848235</v>
       </c>
       <c r="B2" t="n">
-        <v>100798</v>
+        <v>100799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848235</v>
       </c>
       <c r="B2" t="n">
-        <v>100799</v>
+        <v>100800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128848235</v>
       </c>
       <c r="B2" t="n">
-        <v>100800</v>
+        <v>100804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128848230</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128848235</v>
+        <v>128848230</v>
       </c>
       <c r="B2" t="n">
-        <v>100804</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437260</v>
+        <v>437215</v>
       </c>
       <c r="R2" t="n">
-        <v>7004309</v>
+        <v>7004300</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +763,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Örtrik, äldre granskog</t>
+          <t>Tidigare gallrad, örtrik naturskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,37 +781,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128848230</v>
+        <v>128848235</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>101227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437215</v>
+        <v>437260</v>
       </c>
       <c r="R3" t="n">
-        <v>7004300</v>
+        <v>7004309</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Tidigare gallrad, örtrik naturskog</t>
+          <t>Örtrik, äldre granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 47993-2025 artfynd.xlsx
+++ b/artfynd/A 47993-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848230</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,8 +895,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848235</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>